--- a/artfynd/A 290-2025 artfynd.xlsx
+++ b/artfynd/A 290-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122194727</v>
       </c>
       <c r="B2" t="n">
-        <v>91394</v>
+        <v>91404</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 290-2025 artfynd.xlsx
+++ b/artfynd/A 290-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122194727</v>
       </c>
       <c r="B2" t="n">
-        <v>91404</v>
+        <v>91416</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 290-2025 artfynd.xlsx
+++ b/artfynd/A 290-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122194727</v>
       </c>
       <c r="B2" t="n">
-        <v>91416</v>
+        <v>91421</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 290-2025 artfynd.xlsx
+++ b/artfynd/A 290-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122194727</v>
       </c>
       <c r="B2" t="n">
-        <v>91421</v>
+        <v>91426</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>1339</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Brandticka</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Pycnoporellus fulgens</t>
@@ -775,11 +770,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">

--- a/artfynd/A 290-2025 artfynd.xlsx
+++ b/artfynd/A 290-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122194727</v>
       </c>
       <c r="B2" t="n">
-        <v>91426</v>
+        <v>91439</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,6 +693,11 @@
       <c r="E2" t="n">
         <v>1339</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Pycnoporellus fulgens</t>
@@ -770,6 +775,11 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">

--- a/artfynd/A 290-2025 artfynd.xlsx
+++ b/artfynd/A 290-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122194727</v>
       </c>
       <c r="B2" t="n">
-        <v>91439</v>
+        <v>91452</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 290-2025 artfynd.xlsx
+++ b/artfynd/A 290-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>122194727</v>
       </c>
       <c r="B2" t="n">
-        <v>91452</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
